--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F452D90F-72EE-409D-9451-A2A50A38A6E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4D8A1C-0392-4FCD-B5E7-FA3A40BABD6D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33998BC0-1AD2-4E90-B60B-656F5723D10A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28BEA0D5-706B-491F-93CA-DF143996E6B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25009F80-C499-494D-98A6-D74B6E9DD44E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B057416-91DB-4BF5-9B6D-96B563AD93D5}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4D8A1C-0392-4FCD-B5E7-FA3A40BABD6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF8FA816-0D1C-482A-B609-4A2D35F88C83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28BEA0D5-706B-491F-93CA-DF143996E6B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{044801F9-DFFB-48D8-B93E-425DC08E9F4E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B057416-91DB-4BF5-9B6D-96B563AD93D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{322E0263-C0A0-466D-82DD-842E28FE47BF}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF8FA816-0D1C-482A-B609-4A2D35F88C83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A290E386-77A0-47B8-ACBE-B41E25283156}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{044801F9-DFFB-48D8-B93E-425DC08E9F4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BA00F9-9A33-46CD-9F83-308C45870F07}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{322E0263-C0A0-466D-82DD-842E28FE47BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2291ED8A-EFD2-4B49-A2B8-FC3FF679F4C1}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A290E386-77A0-47B8-ACBE-B41E25283156}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F94547-AF82-4D3A-8F9C-0839738F3392}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BA00F9-9A33-46CD-9F83-308C45870F07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176EEB45-A670-4E37-B531-5C0695C05B00}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2291ED8A-EFD2-4B49-A2B8-FC3FF679F4C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C35E456F-92E3-4C80-AE5D-A704E1F86E73}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F94547-AF82-4D3A-8F9C-0839738F3392}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{000D0036-CABA-4CD4-B726-7DAB2D6F6AA5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176EEB45-A670-4E37-B531-5C0695C05B00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8208B2-9E71-4355-AFB9-0470F8C77D2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C35E456F-92E3-4C80-AE5D-A704E1F86E73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CF1878-69CE-470E-BDD7-4D2F7E28FB4F}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{000D0036-CABA-4CD4-B726-7DAB2D6F6AA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23507BD6-D010-4B26-A7B5-9206C5CF9E8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8208B2-9E71-4355-AFB9-0470F8C77D2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C345545B-F0CD-4E59-8674-1635C1863819}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CF1878-69CE-470E-BDD7-4D2F7E28FB4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C141C0-ED5C-4AD1-839A-993970EE57AD}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23507BD6-D010-4B26-A7B5-9206C5CF9E8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E5AB8A-319D-4CC7-ACC0-50F017C9AE73}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C345545B-F0CD-4E59-8674-1635C1863819}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FDA349-C7BA-4ABD-9BC2-E54F5B6587CC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C141C0-ED5C-4AD1-839A-993970EE57AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B161A610-C00D-4A00-8F70-D3D85333F44A}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E5AB8A-319D-4CC7-ACC0-50F017C9AE73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C6A928-2407-40DD-BB8D-75064E2BB685}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FDA349-C7BA-4ABD-9BC2-E54F5B6587CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F2BDC1-0986-4E98-B726-661A5E7FE398}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B161A610-C00D-4A00-8F70-D3D85333F44A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4372A347-E195-4DB8-8A58-8BA770C1F22A}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Table4.1_snapshot.xlsx
@@ -1640,13 +1640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C6A928-2407-40DD-BB8D-75064E2BB685}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AFCDFDE-AD97-44E5-A981-7E7DD9922E89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F2BDC1-0986-4E98-B726-661A5E7FE398}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967B2580-632D-4EBE-B2B0-F47DC57871D0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4372A347-E195-4DB8-8A58-8BA770C1F22A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2909B951-4A1E-4FDA-9A33-414ECD0D6C9C}"/>
 </file>